--- a/data/trans_orig/CoTrAQ-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37576</t>
+          <t>38588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>29138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>59023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33394</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65629</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86353</t>
+          <t>87138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47309</t>
+          <t>47904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65840</t>
+          <t>65616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118939</t>
+          <t>120052</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>147358</t>
+          <t>149063</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>23768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47941</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>12901</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30391</t>
+          <t>30934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27780</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51417</t>
+          <t>53289</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121265</t>
+          <t>120255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142730</t>
+          <t>142618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68542</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89766</t>
+          <t>90150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197770</t>
+          <t>197625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>227183</t>
+          <t>225746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>31235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25773</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46071</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90526</t>
+          <t>90481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111539</t>
+          <t>111634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>39858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56261</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>134332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162097</t>
+          <t>161090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>43264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34164</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29077</t>
+          <t>29935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52792</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93154</t>
+          <t>91260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114063</t>
+          <t>114783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57273</t>
+          <t>56218</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76004</t>
+          <t>75280</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>155142</t>
+          <t>155052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184567</t>
+          <t>184481</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>29038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49808</t>
+          <t>50648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>36746</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39542</t>
+          <t>39983</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57363</t>
+          <t>57996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57004</t>
+          <t>57820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81190</t>
+          <t>81786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>22388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>31490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37945</t>
+          <t>38491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71907</t>
+          <t>70603</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91715</t>
+          <t>91103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35420</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112071</t>
+          <t>111297</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>134625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>26522</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50270</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41914</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52911</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83333</t>
+          <t>85217</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>31115</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55675</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49816</t>
+          <t>50535</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>65885</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>100095</t>
+          <t>97599</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>165002</t>
+          <t>165600</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196407</t>
+          <t>195827</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>90173</t>
+          <t>90430</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116775</t>
+          <t>118248</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>264038</t>
+          <t>264158</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304909</t>
+          <t>305659</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>25843</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51235</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>65574</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>102163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>44863</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>74283</t>
+          <t>75657</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>57830</t>
+          <t>56213</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>83631</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>121175</t>
+          <t>122962</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>233620</t>
+          <t>232913</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>268990</t>
+          <t>269938</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>156853</t>
+          <t>156379</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>187139</t>
+          <t>188651</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>403715</t>
+          <t>400685</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>448994</t>
+          <t>447903</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>157107</t>
+          <t>159502</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>210326</t>
+          <t>214712</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>130100</t>
+          <t>132265</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>178100</t>
+          <t>181322</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>303929</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>377817</t>
+          <t>375033</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>188932</t>
+          <t>190051</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>247193</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>135744</t>
+          <t>134966</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>182130</t>
+          <t>179078</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>338714</t>
+          <t>337359</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>410745</t>
+          <t>411728</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>944619</t>
+          <t>944768</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1016884</t>
+          <t>1016177</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>562098</t>
+          <t>563741</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>620915</t>
+          <t>621024</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1525136</t>
+          <t>1521554</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1613385</t>
+          <t>1616962</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62458</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38979</t>
+          <t>39690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66347</t>
+          <t>65670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96963</t>
+          <t>97342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33164</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31653</t>
+          <t>32020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55723</t>
+          <t>56006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54375</t>
+          <t>55108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79818</t>
+          <t>79615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37378</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58270</t>
+          <t>57371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97361</t>
+          <t>96087</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>128962</t>
+          <t>129914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>29028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>52175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20662</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38667</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55158</t>
+          <t>53693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83789</t>
+          <t>85059</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28876</t>
+          <t>29438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52242</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17717</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34913</t>
+          <t>35367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>51084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80942</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77558</t>
+          <t>78576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105316</t>
+          <t>105912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70099</t>
+          <t>70409</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134996</t>
+          <t>132158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168040</t>
+          <t>167638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>40477</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29619</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40133</t>
+          <t>39881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63688</t>
+          <t>63303</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>34975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79439</t>
+          <t>79605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>44873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65515</t>
+          <t>65601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45745</t>
+          <t>46316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79662</t>
+          <t>78739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106337</t>
+          <t>106381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>25904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>25646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>49394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20877</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>30826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70835</t>
+          <t>71655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91652</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47025</t>
+          <t>47067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63942</t>
+          <t>63719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121171</t>
+          <t>122876</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149593</t>
+          <t>150424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30185</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45386</t>
+          <t>44364</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56690</t>
+          <t>55782</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>37103</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66608</t>
+          <t>66886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88559</t>
+          <t>88698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>35998</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37695</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61129</t>
+          <t>61420</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>39694</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>35103</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43122</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>69811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61486</t>
+          <t>61166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>36270</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>66742</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92216</t>
+          <t>92450</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>123066</t>
+          <t>125081</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163572</t>
+          <t>164719</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>113148</t>
+          <t>113341</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148925</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246464</t>
+          <t>246033</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>300615</t>
+          <t>297967</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72604</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107525</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>73230</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>126469</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>170514</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>107704</t>
+          <t>109790</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145855</t>
+          <t>148943</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>78348</t>
+          <t>80043</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>111835</t>
+          <t>112891</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>200334</t>
+          <t>199886</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>252499</t>
+          <t>249419</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -8263,12 +8263,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36089</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49024</t>
+          <t>48016</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>47578</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77524</t>
+          <t>76506</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>40422</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>66380</t>
+          <t>68314</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8411,12 +8411,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>52547</t>
+          <t>53474</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>77224</t>
+          <t>75142</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>113514</t>
+          <t>111641</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>234719</t>
+          <t>235647</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>265421</t>
+          <t>265834</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>149669</t>
+          <t>148408</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>179045</t>
+          <t>177121</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>393481</t>
+          <t>392896</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>436463</t>
+          <t>438248</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>310145</t>
+          <t>312169</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>377952</t>
+          <t>377903</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>268682</t>
+          <t>269613</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>328058</t>
+          <t>329225</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>600016</t>
+          <t>597361</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>689283</t>
+          <t>688323</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>273836</t>
+          <t>273677</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>338540</t>
+          <t>335916</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>198462</t>
+          <t>196384</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>249988</t>
+          <t>250339</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>486137</t>
+          <t>484041</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>564097</t>
+          <t>573467</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>736066</t>
+          <t>737475</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>812043</t>
+          <t>811516</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8980,12 +8980,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>484910</t>
+          <t>485112</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>549948</t>
+          <t>549827</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1239983</t>
+          <t>1244271</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1340572</t>
+          <t>1340367</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoTrAQ-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18563</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33978</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59023</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64857</t>
+          <t>66274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87138</t>
+          <t>87018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65616</t>
+          <t>64524</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>120052</t>
+          <t>119535</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149063</t>
+          <t>146982</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>28372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>24609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>47623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27421</t>
+          <t>27725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30934</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29512</t>
+          <t>29121</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>52278</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120255</t>
+          <t>120824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142618</t>
+          <t>142527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69889</t>
+          <t>68575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90150</t>
+          <t>89436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197625</t>
+          <t>196630</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225746</t>
+          <t>226622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24946</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31235</t>
+          <t>31678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>45943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90481</t>
+          <t>90698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111634</t>
+          <t>110785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55830</t>
+          <t>55981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134332</t>
+          <t>135889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161090</t>
+          <t>161445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>19379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15455</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29935</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>53299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91260</t>
+          <t>92387</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114783</t>
+          <t>114030</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56218</t>
+          <t>57196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75280</t>
+          <t>75991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>155052</t>
+          <t>156202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184481</t>
+          <t>184776</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50648</t>
+          <t>50138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18590</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36746</t>
+          <t>36859</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57996</t>
+          <t>59447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81786</t>
+          <t>82019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,83%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>31244</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38491</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70603</t>
+          <t>72956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91103</t>
+          <t>91911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>35919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47433</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111297</t>
+          <t>110609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>134625</t>
+          <t>134743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41751</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52911</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85217</t>
+          <t>84797</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31115</t>
+          <t>31097</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55333</t>
+          <t>56443</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27599</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>64296</t>
+          <t>63117</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>97599</t>
+          <t>96844</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>165600</t>
+          <t>164074</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>195827</t>
+          <t>196335</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>90430</t>
+          <t>91215</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118248</t>
+          <t>117458</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>264158</t>
+          <t>263394</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>305659</t>
+          <t>305499</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59269</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65574</t>
+          <t>67118</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>102163</t>
+          <t>100638</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44863</t>
+          <t>46146</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75657</t>
+          <t>75436</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>56213</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>83811</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>122962</t>
+          <t>120918</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>232913</t>
+          <t>233790</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>269938</t>
+          <t>268232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>156379</t>
+          <t>155283</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>188651</t>
+          <t>186969</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>400685</t>
+          <t>402749</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>447903</t>
+          <t>449101</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>159502</t>
+          <t>159331</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>214712</t>
+          <t>209965</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>132265</t>
+          <t>131060</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>181322</t>
+          <t>178080</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>304159</t>
+          <t>305181</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>375033</t>
+          <t>373668</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>190051</t>
+          <t>189788</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>247193</t>
+          <t>246228</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>134966</t>
+          <t>136060</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>179078</t>
+          <t>184050</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>333165</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>411728</t>
+          <t>411520</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>944768</t>
+          <t>945134</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1016177</t>
+          <t>1012419</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>563741</t>
+          <t>562357</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>621024</t>
+          <t>620636</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1521554</t>
+          <t>1526867</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1616962</t>
+          <t>1620120</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39162</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>63246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>21053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39690</t>
+          <t>39145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65670</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97342</t>
+          <t>97578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56006</t>
+          <t>55935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79615</t>
+          <t>78823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36462</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57371</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96087</t>
+          <t>97243</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>129914</t>
+          <t>130163</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>28405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52175</t>
+          <t>50433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19762</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>37785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53693</t>
+          <t>54343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85059</t>
+          <t>83283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17905</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>35544</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>51332</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80863</t>
+          <t>80154</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78576</t>
+          <t>78415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>104422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>48800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70409</t>
+          <t>69461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132158</t>
+          <t>134860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167638</t>
+          <t>168954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40477</t>
+          <t>40274</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39881</t>
+          <t>40388</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63303</t>
+          <t>64519</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31725</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51399</t>
+          <t>52255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54346</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79605</t>
+          <t>81251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44873</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65601</t>
+          <t>65777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>27960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46316</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78739</t>
+          <t>77701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106381</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>28842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25646</t>
+          <t>25769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49394</t>
+          <t>48123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>21633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71655</t>
+          <t>69115</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>90180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47067</t>
+          <t>47077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63719</t>
+          <t>65242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122876</t>
+          <t>123988</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>150424</t>
+          <t>149059</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34749</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44364</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55782</t>
+          <t>57094</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37103</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66886</t>
+          <t>65936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88698</t>
+          <t>88938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>17604</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>36038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7366,82 +7366,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>33,52%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>22289</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>14601</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>30043</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>48832</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>37169</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>61318</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>26,67%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>33,49%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>22289</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>14971</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>30581</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>48832</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>37916</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>61420</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>20,71%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39694</t>
+          <t>39210</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35103</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69811</t>
+          <t>67517</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41453</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61166</t>
+          <t>62200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66742</t>
+          <t>65419</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92450</t>
+          <t>93171</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>125081</t>
+          <t>123955</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>164719</t>
+          <t>163065</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>113341</t>
+          <t>115141</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>149030</t>
+          <t>147731</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246033</t>
+          <t>244528</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>297967</t>
+          <t>297286</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71851</t>
+          <t>72603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108510</t>
+          <t>109302</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44080</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71697</t>
+          <t>72718</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126469</t>
+          <t>126243</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>170371</t>
+          <t>169945</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>148943</t>
+          <t>146198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>80043</t>
+          <t>79112</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112891</t>
+          <t>111568</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>199886</t>
+          <t>198370</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>249419</t>
+          <t>251303</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -8263,12 +8263,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>36106</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48016</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47578</t>
+          <t>46687</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76506</t>
+          <t>74982</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>68314</t>
+          <t>66769</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8411,12 +8411,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>53474</t>
+          <t>52471</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>75142</t>
+          <t>75914</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>111641</t>
+          <t>111193</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>235647</t>
+          <t>236773</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>265834</t>
+          <t>265711</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>148408</t>
+          <t>149990</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>177121</t>
+          <t>178009</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>392896</t>
+          <t>395466</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>438248</t>
+          <t>436880</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,73%</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>312169</t>
+          <t>310752</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>377903</t>
+          <t>377615</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>269613</t>
+          <t>271231</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>329225</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>597361</t>
+          <t>599114</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>688323</t>
+          <t>687936</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>273677</t>
+          <t>275003</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>335916</t>
+          <t>334427</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>196384</t>
+          <t>194801</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>250339</t>
+          <t>250623</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>484041</t>
+          <t>484770</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>573467</t>
+          <t>567940</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>737475</t>
+          <t>736907</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>811516</t>
+          <t>811385</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8980,12 +8980,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>485112</t>
+          <t>483378</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>549827</t>
+          <t>554116</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1244271</t>
+          <t>1236812</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1340367</t>
+          <t>1340746</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
